--- a/traitement-erreur/ig/CdaSTEDONToStringConceptMap.xlsx
+++ b/traitement-erreur/ig/CdaSTEDONToStringConceptMap.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T09:26:13+00:00</t>
+    <t>2026-07-22T09:42:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/traitement-erreur/ig/CdaSTEDONToStringConceptMap.xlsx
+++ b/traitement-erreur/ig/CdaSTEDONToStringConceptMap.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T09:42:41+00:00</t>
+    <t>2026-07-22T12:41:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/traitement-erreur/ig/CdaSTEDONToStringConceptMap.xlsx
+++ b/traitement-erreur/ig/CdaSTEDONToStringConceptMap.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T12:41:23+00:00</t>
+    <t>2026-07-22T12:48:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/traitement-erreur/ig/CdaSTEDONToStringConceptMap.xlsx
+++ b/traitement-erreur/ig/CdaSTEDONToStringConceptMap.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T12:48:49+00:00</t>
+    <t>2026-07-22T12:56:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/traitement-erreur/ig/CdaSTEDONToStringConceptMap.xlsx
+++ b/traitement-erreur/ig/CdaSTEDONToStringConceptMap.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T12:56:04+00:00</t>
+    <t>2026-07-22T13:03:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/traitement-erreur/ig/CdaSTEDONToStringConceptMap.xlsx
+++ b/traitement-erreur/ig/CdaSTEDONToStringConceptMap.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T13:03:41+00:00</t>
+    <t>2026-07-22T13:13:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/traitement-erreur/ig/CdaSTEDONToStringConceptMap.xlsx
+++ b/traitement-erreur/ig/CdaSTEDONToStringConceptMap.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T13:13:54+00:00</t>
+    <t>2026-07-22T13:17:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/traitement-erreur/ig/CdaSTEDONToStringConceptMap.xlsx
+++ b/traitement-erreur/ig/CdaSTEDONToStringConceptMap.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T13:17:03+00:00</t>
+    <t>2026-07-22T13:34:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/traitement-erreur/ig/CdaSTEDONToStringConceptMap.xlsx
+++ b/traitement-erreur/ig/CdaSTEDONToStringConceptMap.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T13:34:22+00:00</t>
+    <t>2026-07-22T13:44:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/traitement-erreur/ig/CdaSTEDONToStringConceptMap.xlsx
+++ b/traitement-erreur/ig/CdaSTEDONToStringConceptMap.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T13:44:26+00:00</t>
+    <t>2026-07-22T13:54:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/traitement-erreur/ig/CdaSTEDONToStringConceptMap.xlsx
+++ b/traitement-erreur/ig/CdaSTEDONToStringConceptMap.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="44">
   <si>
     <t>Property</t>
   </si>
@@ -26,7 +26,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/mappingcdafhir/ConceptMap/DataTypes/CdaStringTypesToFHIR</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/mappingcdafhir/ConceptMap/CdaSTEDONToStringConceptMap</t>
   </si>
   <si>
     <t>Version</t>
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T13:54:49+00:00</t>
+    <t>2026-07-22T14:05:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -119,25 +119,34 @@
     <t>ST.xmlText</t>
   </si>
   <si>
+    <t>Allows for mixed text content</t>
+  </si>
+  <si>
     <t>equivalent</t>
   </si>
   <si>
     <t>string</t>
   </si>
   <si>
+    <t>Primitive Type string</t>
+  </si>
+  <si>
     <t>http://hl7.org/cda/stds/core/StructureDefinition/ED|2.0.0-sd</t>
   </si>
   <si>
     <t>ED.xmlText</t>
   </si>
   <si>
+    <t>Allows for mixed text content. If @representation='B64', this SHALL be a base64binary string.</t>
+  </si>
+  <si>
     <t>related-to</t>
   </si>
   <si>
     <t>http://hl7.org/cda/stds/core/StructureDefinition/ON|2.0.0-sd</t>
   </si>
   <si>
-    <t>ON.xmlText</t>
+    <t>ON.item.xmlText</t>
   </si>
 </sst>
 </file>
@@ -435,16 +444,16 @@
         <v>33</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E3" t="s" s="2">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -476,7 +485,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>31</v>
@@ -493,19 +502,19 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="C3" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="D3" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="E3" t="s" s="2">
         <v>37</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="C3" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D3" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="E3" t="s" s="2">
-        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -537,7 +546,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>31</v>
@@ -554,19 +563,19 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E3" t="s" s="2">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/traitement-erreur/ig/CdaSTEDONToStringConceptMap.xlsx
+++ b/traitement-erreur/ig/CdaSTEDONToStringConceptMap.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T14:05:46+00:00</t>
+    <t>2026-07-22T14:07:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/traitement-erreur/ig/CdaSTEDONToStringConceptMap.xlsx
+++ b/traitement-erreur/ig/CdaSTEDONToStringConceptMap.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T14:07:48+00:00</t>
+    <t>2026-07-22T14:16:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/traitement-erreur/ig/CdaSTEDONToStringConceptMap.xlsx
+++ b/traitement-erreur/ig/CdaSTEDONToStringConceptMap.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T14:16:03+00:00</t>
+    <t>2026-07-22T14:21:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/traitement-erreur/ig/CdaSTEDONToStringConceptMap.xlsx
+++ b/traitement-erreur/ig/CdaSTEDONToStringConceptMap.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T14:21:54+00:00</t>
+    <t>2026-07-23T07:32:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/traitement-erreur/ig/CdaSTEDONToStringConceptMap.xlsx
+++ b/traitement-erreur/ig/CdaSTEDONToStringConceptMap.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T07:32:26+00:00</t>
+    <t>2026-07-23T08:14:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/traitement-erreur/ig/CdaSTEDONToStringConceptMap.xlsx
+++ b/traitement-erreur/ig/CdaSTEDONToStringConceptMap.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T08:14:58+00:00</t>
+    <t>2026-07-23T08:59:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/traitement-erreur/ig/CdaSTEDONToStringConceptMap.xlsx
+++ b/traitement-erreur/ig/CdaSTEDONToStringConceptMap.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T08:59:18+00:00</t>
+    <t>2026-07-23T09:17:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/traitement-erreur/ig/CdaSTEDONToStringConceptMap.xlsx
+++ b/traitement-erreur/ig/CdaSTEDONToStringConceptMap.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T09:17:16+00:00</t>
+    <t>2026-07-23T09:29:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/traitement-erreur/ig/CdaSTEDONToStringConceptMap.xlsx
+++ b/traitement-erreur/ig/CdaSTEDONToStringConceptMap.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T09:29:57+00:00</t>
+    <t>2026-07-23T09:46:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/traitement-erreur/ig/CdaSTEDONToStringConceptMap.xlsx
+++ b/traitement-erreur/ig/CdaSTEDONToStringConceptMap.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T09:46:45+00:00</t>
+    <t>2026-07-23T09:53:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/traitement-erreur/ig/CdaSTEDONToStringConceptMap.xlsx
+++ b/traitement-erreur/ig/CdaSTEDONToStringConceptMap.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T09:53:42+00:00</t>
+    <t>2026-07-23T11:57:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/traitement-erreur/ig/CdaSTEDONToStringConceptMap.xlsx
+++ b/traitement-erreur/ig/CdaSTEDONToStringConceptMap.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T11:57:58+00:00</t>
+    <t>2026-07-23T12:15:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/traitement-erreur/ig/CdaSTEDONToStringConceptMap.xlsx
+++ b/traitement-erreur/ig/CdaSTEDONToStringConceptMap.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T12:15:47+00:00</t>
+    <t>2026-07-23T12:46:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/traitement-erreur/ig/CdaSTEDONToStringConceptMap.xlsx
+++ b/traitement-erreur/ig/CdaSTEDONToStringConceptMap.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T12:46:45+00:00</t>
+    <t>2026-07-23T13:24:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/traitement-erreur/ig/CdaSTEDONToStringConceptMap.xlsx
+++ b/traitement-erreur/ig/CdaSTEDONToStringConceptMap.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T13:24:07+00:00</t>
+    <t>2026-07-23T13:43:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/traitement-erreur/ig/CdaSTEDONToStringConceptMap.xlsx
+++ b/traitement-erreur/ig/CdaSTEDONToStringConceptMap.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T13:43:57+00:00</t>
+    <t>2026-07-24T10:16:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/traitement-erreur/ig/CdaSTEDONToStringConceptMap.xlsx
+++ b/traitement-erreur/ig/CdaSTEDONToStringConceptMap.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-24T10:16:52+00:00</t>
+    <t>2026-07-28T10:59:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/traitement-erreur/ig/CdaSTEDONToStringConceptMap.xlsx
+++ b/traitement-erreur/ig/CdaSTEDONToStringConceptMap.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T10:59:15+00:00</t>
+    <t>2026-07-28T11:21:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/traitement-erreur/ig/CdaSTEDONToStringConceptMap.xlsx
+++ b/traitement-erreur/ig/CdaSTEDONToStringConceptMap.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T11:21:01+00:00</t>
+    <t>2026-07-28T11:32:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/traitement-erreur/ig/CdaSTEDONToStringConceptMap.xlsx
+++ b/traitement-erreur/ig/CdaSTEDONToStringConceptMap.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T11:32:15+00:00</t>
+    <t>2026-07-30T13:25:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/traitement-erreur/ig/CdaSTEDONToStringConceptMap.xlsx
+++ b/traitement-erreur/ig/CdaSTEDONToStringConceptMap.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T13:25:45+00:00</t>
+    <t>2026-07-30T13:42:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/traitement-erreur/ig/CdaSTEDONToStringConceptMap.xlsx
+++ b/traitement-erreur/ig/CdaSTEDONToStringConceptMap.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T13:42:30+00:00</t>
+    <t>2026-07-30T13:43:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/traitement-erreur/ig/CdaSTEDONToStringConceptMap.xlsx
+++ b/traitement-erreur/ig/CdaSTEDONToStringConceptMap.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T13:43:48+00:00</t>
+    <t>2026-07-30T13:49:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/traitement-erreur/ig/CdaSTEDONToStringConceptMap.xlsx
+++ b/traitement-erreur/ig/CdaSTEDONToStringConceptMap.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T13:49:22+00:00</t>
+    <t>2026-07-31T12:53:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
